--- a/data/ready_stocks/ad-ozon-stocks-updated.xlsx
+++ b/data/ready_stocks/ad-ozon-stocks-updated.xlsx
@@ -536,7 +536,7 @@
         <v/>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -550,7 +550,7 @@
         <v/>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -578,7 +578,7 @@
         <v/>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -690,7 +690,7 @@
         <v/>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -788,7 +788,7 @@
         <v/>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -802,7 +802,7 @@
         <v/>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -886,7 +886,7 @@
         <v/>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -998,7 +998,7 @@
         <v/>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1040,7 +1040,7 @@
         <v/>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1222,7 +1222,7 @@
         <v/>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1404,7 +1404,7 @@
         <v/>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1530,7 +1530,7 @@
         <v/>
       </c>
       <c r="D81">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1852,7 +1852,7 @@
         <v/>
       </c>
       <c r="D104">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -1866,7 +1866,7 @@
         <v/>
       </c>
       <c r="D105">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -1936,7 +1936,7 @@
         <v/>
       </c>
       <c r="D110">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -1964,7 +1964,7 @@
         <v/>
       </c>
       <c r="D112">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2034,7 +2034,7 @@
         <v/>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
@@ -2076,7 +2076,7 @@
         <v/>
       </c>
       <c r="D120">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2230,7 +2230,7 @@
         <v/>
       </c>
       <c r="D131">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2370,7 +2370,7 @@
         <v/>
       </c>
       <c r="D141">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -2412,7 +2412,7 @@
         <v/>
       </c>
       <c r="D144">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -2440,7 +2440,7 @@
         <v/>
       </c>
       <c r="D146">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -2468,7 +2468,7 @@
         <v/>
       </c>
       <c r="D148">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -2538,7 +2538,7 @@
         <v/>
       </c>
       <c r="D153">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -2552,7 +2552,7 @@
         <v/>
       </c>
       <c r="D154">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/ready_stocks/ad-ozon-stocks-updated.xlsx
+++ b/data/ready_stocks/ad-ozon-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D153"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,13 +418,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B2" t="str">
-        <v>AD-220120-VishiOSN-8</v>
+        <v>AD-220120-DomUyutOSN-8</v>
       </c>
       <c r="C2" t="str">
         <v/>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -432,13 +432,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B3" t="str">
-        <v>AD-220120-DomUyutOSN-8</v>
+        <v>AD-220120-UltramarinOSN-8</v>
       </c>
       <c r="C3" t="str">
         <v/>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -446,13 +446,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B4" t="str">
-        <v>AD-220120-UltramarinOSN-8</v>
+        <v>AD-220120-KapigusiOSN-8</v>
       </c>
       <c r="C4" t="str">
         <v/>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -460,13 +460,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B5" t="str">
-        <v>AD-220120-KapigusiOSN-8</v>
+        <v>AD-220120-KotovasiyaKOMP-8</v>
       </c>
       <c r="C5" t="str">
         <v/>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -474,13 +474,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B6" t="str">
-        <v>AD-220120-KotovasiyaKOMP-8</v>
+        <v>AD-220120-DenimKOMP-8</v>
       </c>
       <c r="C6" t="str">
         <v/>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -488,13 +488,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B7" t="str">
-        <v>AD-220120-DenimKOMP-8</v>
+        <v>AD-220120-StraykKOMP-8</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -502,13 +502,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B8" t="str">
-        <v>AD-220120-StraykKOMP-8</v>
+        <v>AD-220120-DenimOSN-8</v>
       </c>
       <c r="C8" t="str">
         <v/>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -516,13 +516,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B9" t="str">
-        <v>AD-220120-DenimOSN-8</v>
+        <v>AD-220120-SenorKOMP-8</v>
       </c>
       <c r="C9" t="str">
         <v/>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -530,7 +530,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B10" t="str">
-        <v>AD-220120-SenorKOMP-8</v>
+        <v>AD-220120-DomUyutKOMP-8</v>
       </c>
       <c r="C10" t="str">
         <v/>
@@ -544,7 +544,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B11" t="str">
-        <v>AD-220120-DomUyutKOMP-8</v>
+        <v>AD-220120-IntonatsiyaKOMP-8</v>
       </c>
       <c r="C11" t="str">
         <v/>
@@ -558,13 +558,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B12" t="str">
-        <v>AD-220120-IntonatsiyaKOMP-8</v>
+        <v>AD-220120-RomansOSN-8</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
       <c r="D12">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -572,7 +572,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B13" t="str">
-        <v>AD-220120-RomansOSN-8</v>
+        <v>AD-220120-ShyelkOSN-8</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -586,13 +586,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B14" t="str">
-        <v>AD-220120-ShyelkOSN-8</v>
+        <v>AD-220120-AlbertOSN-8</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
       <c r="D14">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -600,13 +600,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B15" t="str">
-        <v>AD-220120-AlbertOSN-8</v>
+        <v>AD-220120-BenefisKOMP-8</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -614,13 +614,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B16" t="str">
-        <v>AD-220120-BenefisKOMP-8</v>
+        <v>AD-220120-GarmoniyaOSN-8</v>
       </c>
       <c r="C16" t="str">
         <v/>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -628,13 +628,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B17" t="str">
-        <v>AD-220120-GarmoniyaOSN-8</v>
+        <v>AD-220120-IridaOSN-8</v>
       </c>
       <c r="C17" t="str">
         <v/>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -642,7 +642,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B18" t="str">
-        <v>AD-220120-IridaOSN-8</v>
+        <v>AD-220120-VishneviySadOSN-8</v>
       </c>
       <c r="C18" t="str">
         <v/>
@@ -656,13 +656,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B19" t="str">
-        <v>AD-220120-VishneviySadOSN-8</v>
+        <v>AD-220120-EffektOSN-8</v>
       </c>
       <c r="C19" t="str">
         <v/>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -670,13 +670,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B20" t="str">
-        <v>AD-220120-EffektOSN-8</v>
+        <v>AD-220120-BelkantoKOMP-8</v>
       </c>
       <c r="C20" t="str">
         <v/>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -684,7 +684,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B21" t="str">
-        <v>AD-220120-BelkantoKOMP-8</v>
+        <v>AD-220120-ElbrusKOMP-8</v>
       </c>
       <c r="C21" t="str">
         <v/>
@@ -698,13 +698,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B22" t="str">
-        <v>AD-220120-ElbrusKOMP-8</v>
+        <v>AD-220120-MagnoliyaKOMP-8</v>
       </c>
       <c r="C22" t="str">
         <v/>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -712,13 +712,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B23" t="str">
-        <v>AD-220120-MagnoliyaKOMP-8</v>
+        <v>AD-220120-BenefisOSN-8</v>
       </c>
       <c r="C23" t="str">
         <v/>
       </c>
       <c r="D23">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -726,13 +726,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B24" t="str">
-        <v>AD-220120-BenefisOSN-8</v>
+        <v>AD-220120-RodosKOMP-8</v>
       </c>
       <c r="C24" t="str">
         <v/>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -740,13 +740,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B25" t="str">
-        <v>AD-220120-RodosKOMP-8</v>
+        <v>AD-220120-StraykOSN-8</v>
       </c>
       <c r="C25" t="str">
         <v/>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -754,13 +754,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B26" t="str">
-        <v>AD-220120-StraykOSN-8</v>
+        <v>AD-220120-MurritoKOMP-8</v>
       </c>
       <c r="C26" t="str">
         <v/>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -768,13 +768,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B27" t="str">
-        <v>AD-220120-MurritoKOMP-8</v>
+        <v>AD-220120-KameoOSN-8</v>
       </c>
       <c r="C27" t="str">
         <v/>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -782,7 +782,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B28" t="str">
-        <v>AD-220120-KameoOSN-8</v>
+        <v>AD-220120-AzaliyaKOMP-8</v>
       </c>
       <c r="C28" t="str">
         <v/>
@@ -796,7 +796,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B29" t="str">
-        <v>AD-220120-AzaliyaKOMP-8</v>
+        <v>AD-220120-SmaylOSN-8</v>
       </c>
       <c r="C29" t="str">
         <v/>
@@ -810,13 +810,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B30" t="str">
-        <v>AD-220120-SmaylOSN-8</v>
+        <v>AD-220120-ModistkaOSN-8</v>
       </c>
       <c r="C30" t="str">
         <v/>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -824,13 +824,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B31" t="str">
-        <v>AD-220120-ModistkaOSN-8</v>
+        <v>AD-220120-Korsika-8</v>
       </c>
       <c r="C31" t="str">
         <v/>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -838,13 +838,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B32" t="str">
-        <v>AD-220120-Korsika-8</v>
+        <v>AD-220120-ShikOSN-8</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -852,13 +852,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B33" t="str">
-        <v>AD-220120-ShikOSN-8</v>
+        <v>AD-220120-TerriKOMP-8</v>
       </c>
       <c r="C33" t="str">
         <v/>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -866,13 +866,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B34" t="str">
-        <v>AD-220120-TerriKOMP-8</v>
+        <v>AD-220120-Enigma-8</v>
       </c>
       <c r="C34" t="str">
         <v/>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -880,13 +880,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B35" t="str">
-        <v>AD-220120-Enigma-8</v>
+        <v>AD-220120-TsvetokZhelaniyKOMP-8</v>
       </c>
       <c r="C35" t="str">
         <v/>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -894,13 +894,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B36" t="str">
-        <v>AD-220120-TsvetokZhelaniyKOMP-8</v>
+        <v>AD-220120-SherriOSN-8</v>
       </c>
       <c r="C36" t="str">
         <v/>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -908,13 +908,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B37" t="str">
-        <v>AD-220120-SherriOSN-8</v>
+        <v>AD-220120-SaraOSN-8</v>
       </c>
       <c r="C37" t="str">
         <v/>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -922,13 +922,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B38" t="str">
-        <v>AD-220120-SaraOSN-8</v>
+        <v>AD-220120-YasminaOSN-8</v>
       </c>
       <c r="C38" t="str">
         <v/>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -936,13 +936,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B39" t="str">
-        <v>AD-220120-YasminaOSN-8</v>
+        <v>AD-220120-ZhenevaOSN-8</v>
       </c>
       <c r="C39" t="str">
         <v/>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -950,13 +950,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B40" t="str">
-        <v>AD-220120-ZhenevaOSN-8</v>
+        <v>AD-220120-KameoKOMP-8</v>
       </c>
       <c r="C40" t="str">
         <v/>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -964,13 +964,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B41" t="str">
-        <v>AD-220120-KameoKOMP-8</v>
+        <v>AD-220120-Glamur-8</v>
       </c>
       <c r="C41" t="str">
         <v/>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -978,13 +978,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B42" t="str">
-        <v>AD-220120-Glamur-8</v>
+        <v>AD-220120-SevernayaKoronaOSN-8</v>
       </c>
       <c r="C42" t="str">
         <v/>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -992,7 +992,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B43" t="str">
-        <v>AD-220120-SevernayaKoronaOSN-8</v>
+        <v>AD-220120-AntuanettaOSN-8</v>
       </c>
       <c r="C43" t="str">
         <v/>
@@ -1006,13 +1006,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B44" t="str">
-        <v>AD-220120-AntuanettaOSN-8</v>
+        <v>AD-220120-SerebryanList-8</v>
       </c>
       <c r="C44" t="str">
         <v/>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1020,13 +1020,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B45" t="str">
-        <v>AD-220120-SerebryanList-8</v>
+        <v>AD-220120-IridaKOMP-8</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1034,7 +1034,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B46" t="str">
-        <v>AD-220120-IridaKOMP-8</v>
+        <v>AD-220120-MayronOSN-8</v>
       </c>
       <c r="C46" t="str">
         <v/>
@@ -1048,13 +1048,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B47" t="str">
-        <v>AD-220120-MayronOSN-8</v>
+        <v>AD-220120-ValsKOMP-8</v>
       </c>
       <c r="C47" t="str">
         <v/>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1062,13 +1062,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B48" t="str">
-        <v>AD-220120-ValsKOMP-8</v>
+        <v>AD-220120-NevesomostOSN-8</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1076,13 +1076,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B49" t="str">
-        <v>AD-220120-NevesomostOSN-8</v>
+        <v>AD-220120-dzhoystikKOMP-8</v>
       </c>
       <c r="C49" t="str">
         <v/>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1090,13 +1090,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B50" t="str">
-        <v>AD-220120-dzhoystikKOMP-8</v>
+        <v>AD-220120-AzaliyaOSN-8</v>
       </c>
       <c r="C50" t="str">
         <v/>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1104,7 +1104,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B51" t="str">
-        <v>AD-220120-AzaliyaOSN-8</v>
+        <v>AD-220120-SiestaOSN-8</v>
       </c>
       <c r="C51" t="str">
         <v/>
@@ -1118,13 +1118,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B52" t="str">
-        <v>AD-220120-SiestaOSN-8</v>
+        <v>AD-220120-Astilba-8</v>
       </c>
       <c r="C52" t="str">
         <v/>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1132,13 +1132,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B53" t="str">
-        <v>AD-220120-Astilba-8</v>
+        <v>AD-220120-ShyelkKOMP-8</v>
       </c>
       <c r="C53" t="str">
         <v/>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1146,13 +1146,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B54" t="str">
-        <v>AD-220120-ShyelkKOMP-8</v>
+        <v>AD-220120-RodosOSN-8</v>
       </c>
       <c r="C54" t="str">
         <v/>
       </c>
       <c r="D54">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1160,13 +1160,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B55" t="str">
-        <v>AD-220120-RodosOSN-8</v>
+        <v>AD-220120-PreobrazhenieOSN-8</v>
       </c>
       <c r="C55" t="str">
         <v/>
       </c>
       <c r="D55">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1174,13 +1174,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B56" t="str">
-        <v>AD-220120-PreobrazhenieOSN-8</v>
+        <v>AD-220120-dzhoystikOSN-8</v>
       </c>
       <c r="C56" t="str">
         <v/>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1188,13 +1188,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B57" t="str">
-        <v>AD-220120-dzhoystikOSN-8</v>
+        <v>AD-220120-ShikKOMP-8</v>
       </c>
       <c r="C57" t="str">
         <v/>
       </c>
       <c r="D57">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1202,13 +1202,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B58" t="str">
-        <v>AD-220120-ShikKOMP-8</v>
+        <v>AD-220120-TokioKOMP-8</v>
       </c>
       <c r="C58" t="str">
         <v/>
       </c>
       <c r="D58">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1216,7 +1216,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B59" t="str">
-        <v>AD-220120-TokioKOMP-8</v>
+        <v>AD-220120-GavanOSN-8</v>
       </c>
       <c r="C59" t="str">
         <v/>
@@ -1230,13 +1230,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B60" t="str">
-        <v>AD-220120-GavanOSN-8</v>
+        <v>AD-220120-LorentseKOMP-8</v>
       </c>
       <c r="C60" t="str">
         <v/>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1244,13 +1244,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B61" t="str">
-        <v>AD-220120-LorentseKOMP-8</v>
+        <v>AD-220120-Krasotki-8</v>
       </c>
       <c r="C61" t="str">
         <v/>
       </c>
       <c r="D61">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1258,13 +1258,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B62" t="str">
-        <v>AD-220120-Krasotki-8</v>
+        <v>AD-220120-KapigusiKOMP-8</v>
       </c>
       <c r="C62" t="str">
         <v/>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -1272,13 +1272,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B63" t="str">
-        <v>AD-220120-KapigusiKOMP-8</v>
+        <v>AD-220120-SnegiriOSN-8</v>
       </c>
       <c r="C63" t="str">
         <v/>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -1286,13 +1286,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B64" t="str">
-        <v>AD-220120-SnegiriOSN-8</v>
+        <v>AD-220120-GeyshaOSN-8</v>
       </c>
       <c r="C64" t="str">
         <v/>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1300,7 +1300,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B65" t="str">
-        <v>AD-220120-GeyshaOSN-8</v>
+        <v>AD-220120-GeyshaKOMP-8</v>
       </c>
       <c r="C65" t="str">
         <v/>
@@ -1314,7 +1314,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B66" t="str">
-        <v>AD-220120-GeyshaKOMP-8</v>
+        <v>AD-220120-ElbrusOSN-8</v>
       </c>
       <c r="C66" t="str">
         <v/>
@@ -1328,13 +1328,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B67" t="str">
-        <v>AD-220120-ElbrusOSN-8</v>
+        <v>AD-220120-PegasOSN-8</v>
       </c>
       <c r="C67" t="str">
         <v/>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1342,13 +1342,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B68" t="str">
-        <v>AD-220120-PegasOSN-8</v>
+        <v>AD-220120-IntonatsiyaOSN-8</v>
       </c>
       <c r="C68" t="str">
         <v/>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -1356,13 +1356,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B69" t="str">
-        <v>AD-220120-IntonatsiyaOSN-8</v>
+        <v>AD-220120-SimfoniyaKOMP-8</v>
       </c>
       <c r="C69" t="str">
         <v/>
       </c>
       <c r="D69">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1370,13 +1370,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B70" t="str">
-        <v>AD-220120-SimfoniyaKOMP-8</v>
+        <v>AD-220120-EffektKOMP-8</v>
       </c>
       <c r="C70" t="str">
         <v/>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1384,13 +1384,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B71" t="str">
-        <v>AD-220120-EffektKOMP-8</v>
+        <v>AD-220120-NevesomostKOMP-8</v>
       </c>
       <c r="C71" t="str">
         <v/>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1398,7 +1398,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B72" t="str">
-        <v>AD-220120-NevesomostKOMP-8</v>
+        <v>AD-220120-SonetOSN-8</v>
       </c>
       <c r="C72" t="str">
         <v/>
@@ -1412,13 +1412,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B73" t="str">
-        <v>AD-220120-SonetOSN-8</v>
+        <v>AD-220120-SimvolUdachiOSN-8</v>
       </c>
       <c r="C73" t="str">
         <v/>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1426,13 +1426,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B74" t="str">
-        <v>AD-220120-SimvolUdachiOSN-8</v>
+        <v>AD-220120-SherriKOMP-8</v>
       </c>
       <c r="C74" t="str">
         <v/>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1440,13 +1440,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B75" t="str">
-        <v>AD-220120-SherriKOMP-8</v>
+        <v>AD-220120-SimvolUdachiKOMP-8</v>
       </c>
       <c r="C75" t="str">
         <v/>
       </c>
       <c r="D75">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1454,13 +1454,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B76" t="str">
-        <v>AD-220120-SimvolUdachiKOMP-8</v>
+        <v>AD-220120-VishiKOMP-8</v>
       </c>
       <c r="C76" t="str">
         <v/>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -1468,13 +1468,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B77" t="str">
-        <v>AD-220120-VishiKOMP-8</v>
+        <v>AD-220120-UltramarinKOMP-8</v>
       </c>
       <c r="C77" t="str">
         <v/>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1482,13 +1482,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B78" t="str">
-        <v>AD-220120-UltramarinKOMP-8</v>
+        <v>AD-220120-TokioOSN-8</v>
       </c>
       <c r="C78" t="str">
         <v/>
       </c>
       <c r="D78">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1496,13 +1496,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B79" t="str">
-        <v>AD-220120-TokioOSN-8</v>
+        <v>AD-220120-MagnoliyaOSN-8</v>
       </c>
       <c r="C79" t="str">
         <v/>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1510,13 +1510,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B80" t="str">
-        <v>AD-220120-MagnoliyaOSN-8</v>
+        <v>AD-220120-PalermoKOMP-8</v>
       </c>
       <c r="C80" t="str">
         <v/>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -1524,7 +1524,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B81" t="str">
-        <v>AD-220120-PalermoKOMP-8</v>
+        <v>AD-220120-PolyankaKOMP-8</v>
       </c>
       <c r="C81" t="str">
         <v/>
@@ -1538,13 +1538,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B82" t="str">
-        <v>AD-220120-PolyankaKOMP-8</v>
+        <v>AD-220120-AntuanettaKOMP-8</v>
       </c>
       <c r="C82" t="str">
         <v/>
       </c>
       <c r="D82">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1552,13 +1552,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B83" t="str">
-        <v>AD-220120-AntuanettaKOMP-8</v>
+        <v>AD-220120-SiestaKOMP-8</v>
       </c>
       <c r="C83" t="str">
         <v/>
       </c>
       <c r="D83">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1566,13 +1566,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B84" t="str">
-        <v>AD-220120-SiestaKOMP-8</v>
+        <v>AD-220120-PolyankaOSN-8</v>
       </c>
       <c r="C84" t="str">
         <v/>
       </c>
       <c r="D84">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1580,13 +1580,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B85" t="str">
-        <v>AD-220120-PolyankaOSN-8</v>
+        <v>AD-220120-PegasKOMP-8</v>
       </c>
       <c r="C85" t="str">
         <v/>
       </c>
       <c r="D85">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -1594,13 +1594,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B86" t="str">
-        <v>AD-220120-PegasKOMP-8</v>
+        <v>AD-220120-ZhenevaKOMP-8</v>
       </c>
       <c r="C86" t="str">
         <v/>
       </c>
       <c r="D86">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -1608,13 +1608,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B87" t="str">
-        <v>AD-220120-ZhenevaKOMP-8</v>
+        <v>AD-220120-CharovnitsaKOMP-8</v>
       </c>
       <c r="C87" t="str">
         <v/>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -1622,13 +1622,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B88" t="str">
-        <v>AD-220120-CharovnitsaKOMP-8</v>
+        <v>AD-220120-ValsOSN-8</v>
       </c>
       <c r="C88" t="str">
         <v/>
       </c>
       <c r="D88">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -1636,13 +1636,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B89" t="str">
-        <v>AD-220120-ValsOSN-8</v>
+        <v>AD-220120-ModistkaKOMP-8</v>
       </c>
       <c r="C89" t="str">
         <v/>
       </c>
       <c r="D89">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1650,13 +1650,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B90" t="str">
-        <v>AD-220120-ModistkaKOMP-8</v>
+        <v>AD-220120-SevernayaKoronaKOMP-8</v>
       </c>
       <c r="C90" t="str">
         <v/>
       </c>
       <c r="D90">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -1664,13 +1664,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B91" t="str">
-        <v>AD-220120-SevernayaKoronaKOMP-8</v>
+        <v>AD-220120-KotovasiyaOSN-8</v>
       </c>
       <c r="C91" t="str">
         <v/>
       </c>
       <c r="D91">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1678,13 +1678,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B92" t="str">
-        <v>AD-220120-KotovasiyaOSN-8</v>
+        <v>AD-220120-VishneviySadKOMP-8</v>
       </c>
       <c r="C92" t="str">
         <v/>
       </c>
       <c r="D92">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1692,13 +1692,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B93" t="str">
-        <v>AD-220120-VishneviySadKOMP-8</v>
+        <v>AD-220120-AlbertKOMP-8</v>
       </c>
       <c r="C93" t="str">
         <v/>
       </c>
       <c r="D93">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1706,13 +1706,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B94" t="str">
-        <v>AD-220120-AlbertKOMP-8</v>
+        <v>AD-220120-BelkantoOSN-8</v>
       </c>
       <c r="C94" t="str">
         <v/>
       </c>
       <c r="D94">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -1720,13 +1720,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B95" t="str">
-        <v>AD-220120-BelkantoOSN-8</v>
+        <v>AD-220120-SimfoniyaOSN-8</v>
       </c>
       <c r="C95" t="str">
         <v/>
       </c>
       <c r="D95">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1734,13 +1734,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B96" t="str">
-        <v>AD-220120-SimfoniyaOSN-8</v>
+        <v>AD-220120-SenorOSN-8</v>
       </c>
       <c r="C96" t="str">
         <v/>
       </c>
       <c r="D96">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -1748,13 +1748,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B97" t="str">
-        <v>AD-220120-SenorOSN-8</v>
+        <v>AD-220120-PismoTatyanyOSN-8</v>
       </c>
       <c r="C97" t="str">
         <v/>
       </c>
       <c r="D97">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -1762,7 +1762,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B98" t="str">
-        <v>AD-220120-PismoTatyanyOSN-8</v>
+        <v>AD-220120-GavanKOMP-8</v>
       </c>
       <c r="C98" t="str">
         <v/>
@@ -1776,13 +1776,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B99" t="str">
-        <v>AD-220120-GavanKOMP-8</v>
+        <v>AD-220120-KeniyaOSN-8</v>
       </c>
       <c r="C99" t="str">
         <v/>
       </c>
       <c r="D99">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -1790,13 +1790,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B100" t="str">
-        <v>AD-220120-KeniyaOSN-8</v>
+        <v>AD-220120-YasminaKOMP-8</v>
       </c>
       <c r="C100" t="str">
         <v/>
       </c>
       <c r="D100">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -1804,13 +1804,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B101" t="str">
-        <v>AD-220120-YasminaKOMP-8</v>
+        <v>AD-220120-GarmoniyaKOMP-8</v>
       </c>
       <c r="C101" t="str">
         <v/>
       </c>
       <c r="D101">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -1818,13 +1818,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B102" t="str">
-        <v>AD-220120-GarmoniyaKOMP-8</v>
+        <v>AD-220120-Vilen-8</v>
       </c>
       <c r="C102" t="str">
         <v/>
       </c>
       <c r="D102">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -1832,13 +1832,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B103" t="str">
-        <v>AD-220120-Vilen-8</v>
+        <v>AD-150120-Klaviatura-8</v>
       </c>
       <c r="C103" t="str">
         <v/>
       </c>
       <c r="D103">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -1846,7 +1846,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B104" t="str">
-        <v>AD-150120-Klaviatura-8</v>
+        <v>AD-150120-IgraKomp-8</v>
       </c>
       <c r="C104" t="str">
         <v/>
@@ -1860,7 +1860,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B105" t="str">
-        <v>AD-150120-IgraKomp-8</v>
+        <v>AD-150120-LegolendKomp-8</v>
       </c>
       <c r="C105" t="str">
         <v/>
@@ -1874,13 +1874,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B106" t="str">
-        <v>AD-150120-LegolendKomp-8</v>
+        <v>AD-150120-AvtodromKomp-8</v>
       </c>
       <c r="C106" t="str">
         <v/>
       </c>
       <c r="D106">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -1888,13 +1888,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B107" t="str">
-        <v>AD-150120-AvtodromKomp-8</v>
+        <v>AD-220120-CharovnitsaOSN-8</v>
       </c>
       <c r="C107" t="str">
         <v/>
       </c>
       <c r="D107">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -1902,13 +1902,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B108" t="str">
-        <v>AD-220120-CharovnitsaOSN-8</v>
+        <v>AD-220120-SmaylKOMP-8</v>
       </c>
       <c r="C108" t="str">
         <v/>
       </c>
       <c r="D108">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -1916,13 +1916,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B109" t="str">
-        <v>AD-220120-SmaylKOMP-8</v>
+        <v>AD-220120-KeniyaKOMP-8</v>
       </c>
       <c r="C109" t="str">
         <v/>
       </c>
       <c r="D109">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -1930,7 +1930,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B110" t="str">
-        <v>AD-220120-KeniyaKOMP-8</v>
+        <v>AD-220120-TerriOSN-8</v>
       </c>
       <c r="C110" t="str">
         <v/>
@@ -1944,13 +1944,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B111" t="str">
-        <v>AD-220120-TerriOSN-8</v>
+        <v>AD-150120-LegolendOsn-8</v>
       </c>
       <c r="C111" t="str">
         <v/>
       </c>
       <c r="D111">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -1958,7 +1958,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B112" t="str">
-        <v>AD-150120-LegolendOsn-8</v>
+        <v>AD-150120-PtashkaOsn-8</v>
       </c>
       <c r="C112" t="str">
         <v/>
@@ -1972,13 +1972,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B113" t="str">
-        <v>AD-150120-PtashkaOsn-8</v>
+        <v>AD-220120-LorentseOSN-8</v>
       </c>
       <c r="C113" t="str">
         <v/>
       </c>
       <c r="D113">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -1986,13 +1986,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B114" t="str">
-        <v>AD-220120-LorentseOSN-8</v>
+        <v>AD-220120-SaraKOMP-8</v>
       </c>
       <c r="C114" t="str">
         <v/>
       </c>
       <c r="D114">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2000,13 +2000,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B115" t="str">
-        <v>AD-220120-SaraKOMP-8</v>
+        <v>AD-150120-PtashkaKomp-8</v>
       </c>
       <c r="C115" t="str">
         <v/>
       </c>
       <c r="D115">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2014,13 +2014,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B116" t="str">
-        <v>AD-150120-PtashkaKomp-8</v>
+        <v>AD-150120-MotorchikOsn-8</v>
       </c>
       <c r="C116" t="str">
         <v/>
       </c>
       <c r="D116">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2028,13 +2028,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B117" t="str">
-        <v>AD-150120-MotorchikOsn-8</v>
+        <v>AD-150120-Khokkey-8</v>
       </c>
       <c r="C117" t="str">
         <v/>
       </c>
       <c r="D117">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2042,7 +2042,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B118" t="str">
-        <v>AD-150120-Khokkey-8</v>
+        <v>AD-150120-Detstvo-8</v>
       </c>
       <c r="C118" t="str">
         <v/>
@@ -2056,7 +2056,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B119" t="str">
-        <v>AD-150120-Detstvo-8</v>
+        <v>AD-150120-PenaltiOsn-8</v>
       </c>
       <c r="C119" t="str">
         <v/>
@@ -2070,7 +2070,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B120" t="str">
-        <v>AD-150120-PenaltiOsn-8</v>
+        <v>AD-150120-GoshaOsn-8</v>
       </c>
       <c r="C120" t="str">
         <v/>
@@ -2084,13 +2084,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B121" t="str">
-        <v>AD-150120-GoshaOsn-8</v>
+        <v>AD-150120-UlyetnyemishkiOsn-8</v>
       </c>
       <c r="C121" t="str">
         <v/>
       </c>
       <c r="D121">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2098,13 +2098,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B122" t="str">
-        <v>AD-150120-UlyetnyemishkiOsn-8</v>
+        <v>AD-150120-IgraOsn-8</v>
       </c>
       <c r="C122" t="str">
         <v/>
       </c>
       <c r="D122">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2112,13 +2112,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B123" t="str">
-        <v>AD-150120-IgraOsn-8</v>
+        <v>AD-150120-BarashkiOsn-8</v>
       </c>
       <c r="C123" t="str">
         <v/>
       </c>
       <c r="D123">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2126,13 +2126,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B124" t="str">
-        <v>AD-150120-BarashkiOsn-8</v>
+        <v>AD-150120-UlyetnyemishkiKomp-8</v>
       </c>
       <c r="C124" t="str">
         <v/>
       </c>
       <c r="D124">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2140,7 +2140,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B125" t="str">
-        <v>AD-150120-UlyetnyemishkiKomp-8</v>
+        <v>AD-150120-MiniVecherinkaKomp-8</v>
       </c>
       <c r="C125" t="str">
         <v/>
@@ -2154,7 +2154,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B126" t="str">
-        <v>AD-150120-MiniVecherinkaKomp-8</v>
+        <v>AD-150120-PenaltiKomp-8</v>
       </c>
       <c r="C126" t="str">
         <v/>
@@ -2168,7 +2168,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B127" t="str">
-        <v>AD-150120-PenaltiKomp-8</v>
+        <v>AD-150120-ImidzhKomp-8</v>
       </c>
       <c r="C127" t="str">
         <v/>
@@ -2182,13 +2182,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B128" t="str">
-        <v>AD-150120-ImidzhKomp-8</v>
+        <v>AD-150120-AvtodromOsn-8</v>
       </c>
       <c r="C128" t="str">
         <v/>
       </c>
       <c r="D128">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2196,13 +2196,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B129" t="str">
-        <v>AD-150120-AvtodromOsn-8</v>
+        <v>AD-220120-SnegiriKOMP-8</v>
       </c>
       <c r="C129" t="str">
         <v/>
       </c>
       <c r="D129">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -2210,13 +2210,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B130" t="str">
-        <v>AD-220120-SnegiriKOMP-8</v>
+        <v>AD-220120-RomansKOMP-8</v>
       </c>
       <c r="C130" t="str">
         <v/>
       </c>
       <c r="D130">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -2224,7 +2224,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B131" t="str">
-        <v>AD-220120-RomansKOMP-8</v>
+        <v>AD-150120-Dinopark-8</v>
       </c>
       <c r="C131" t="str">
         <v/>
@@ -2238,13 +2238,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B132" t="str">
-        <v>AD-150120-Dinopark-8</v>
+        <v>AD-150120-BarashkiKomp-8</v>
       </c>
       <c r="C132" t="str">
         <v/>
       </c>
       <c r="D132">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -2252,13 +2252,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B133" t="str">
-        <v>AD-150120-BarashkiKomp-8</v>
+        <v>AD-220120-SonetKOMP-8</v>
       </c>
       <c r="C133" t="str">
         <v/>
       </c>
       <c r="D133">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -2266,13 +2266,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B134" t="str">
-        <v>AD-220120-SonetKOMP-8</v>
+        <v>AD-150120-MorskoyBoyKomp-8</v>
       </c>
       <c r="C134" t="str">
         <v/>
       </c>
       <c r="D134">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2280,7 +2280,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B135" t="str">
-        <v>AD-150120-MorskoyBoyKomp-8</v>
+        <v>AD-150120-NaOpushkeOsn-8</v>
       </c>
       <c r="C135" t="str">
         <v/>
@@ -2294,13 +2294,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B136" t="str">
-        <v>AD-150120-NaOpushkeOsn-8</v>
+        <v>AD-150120-ZamurchatelZhiznKomp-8</v>
       </c>
       <c r="C136" t="str">
         <v/>
       </c>
       <c r="D136">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -2308,13 +2308,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B137" t="str">
-        <v>AD-150120-ZamurchatelZhiznKomp-8</v>
+        <v>AD-150120-ZamurchatelZhiznOsn-8</v>
       </c>
       <c r="C137" t="str">
         <v/>
       </c>
       <c r="D137">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -2322,13 +2322,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B138" t="str">
-        <v>AD-150120-ZamurchatelZhiznOsn-8</v>
+        <v>AD-220120-PalermoOSN-8</v>
       </c>
       <c r="C138" t="str">
         <v/>
       </c>
       <c r="D138">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -2336,13 +2336,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B139" t="str">
-        <v>AD-220120-PalermoOSN-8</v>
+        <v>AD-220120-MurritoOSN-8</v>
       </c>
       <c r="C139" t="str">
         <v/>
       </c>
       <c r="D139">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -2350,13 +2350,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B140" t="str">
-        <v>AD-220120-MurritoOSN-8</v>
+        <v>AD-220120-PreobrazhenieKOMP-8</v>
       </c>
       <c r="C140" t="str">
         <v/>
       </c>
       <c r="D140">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -2364,7 +2364,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B141" t="str">
-        <v>AD-220120-PreobrazhenieKOMP-8</v>
+        <v>AD-220120-MayronKOMP-8</v>
       </c>
       <c r="C141" t="str">
         <v/>
@@ -2378,13 +2378,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B142" t="str">
-        <v>AD-220120-MayronKOMP-8</v>
+        <v>AD-150120-GoshaKomp-8</v>
       </c>
       <c r="C142" t="str">
         <v/>
       </c>
       <c r="D142">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -2392,13 +2392,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B143" t="str">
-        <v>AD-150120-GoshaKomp-8</v>
+        <v>AD-150120-ImidzhOsn-8</v>
       </c>
       <c r="C143" t="str">
         <v/>
       </c>
       <c r="D143">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -2406,7 +2406,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B144" t="str">
-        <v>AD-150120-ImidzhOsn-8</v>
+        <v>AD-150120-Khvostiki-8</v>
       </c>
       <c r="C144" t="str">
         <v/>
@@ -2420,7 +2420,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B145" t="str">
-        <v>AD-150120-Khvostiki-8</v>
+        <v>AD-150120-Stroitel-8</v>
       </c>
       <c r="C145" t="str">
         <v/>
@@ -2434,7 +2434,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B146" t="str">
-        <v>AD-150120-Stroitel-8</v>
+        <v>AD-150120-MorskoyBoyOsn-8</v>
       </c>
       <c r="C146" t="str">
         <v/>
@@ -2448,13 +2448,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B147" t="str">
-        <v>AD-150120-MorskoyBoyOsn-8</v>
+        <v>AD-150120-KolobokOsn-8</v>
       </c>
       <c r="C147" t="str">
         <v/>
       </c>
       <c r="D147">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -2462,7 +2462,7 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B148" t="str">
-        <v>AD-150120-KolobokOsn-8</v>
+        <v>AD-220120-TsvetokZhelaniyOSN-8</v>
       </c>
       <c r="C148" t="str">
         <v/>
@@ -2476,13 +2476,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B149" t="str">
-        <v>AD-220120-TsvetokZhelaniyOSN-8</v>
+        <v>AD-220120-BelyeTsveti-8</v>
       </c>
       <c r="C149" t="str">
         <v/>
       </c>
       <c r="D149">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -2490,13 +2490,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B150" t="str">
-        <v>AD-220120-BelyeTsveti-8</v>
+        <v>AD-150120-KolobokKomp-8</v>
       </c>
       <c r="C150" t="str">
         <v/>
       </c>
       <c r="D150">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -2504,13 +2504,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B151" t="str">
-        <v>AD-150120-KolobokKomp-8</v>
+        <v>AD-150120-MotorchikKomp-8</v>
       </c>
       <c r="C151" t="str">
         <v/>
       </c>
       <c r="D151">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -2518,13 +2518,13 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B152" t="str">
-        <v>AD-150120-MotorchikKomp-8</v>
+        <v>AD-150120-MiniVecherinkaOsn-8</v>
       </c>
       <c r="C152" t="str">
         <v/>
       </c>
       <c r="D152">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -2532,32 +2532,18 @@
         <v>СЦ (Коляново) (1020002072018000)</v>
       </c>
       <c r="B153" t="str">
-        <v>AD-150120-MiniVecherinkaOsn-8</v>
+        <v>AD-150120-NaOpushkeKomp-8</v>
       </c>
       <c r="C153" t="str">
         <v/>
       </c>
       <c r="D153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
-        <v>СЦ (Коляново) (1020002072018000)</v>
-      </c>
-      <c r="B154" t="str">
-        <v>AD-150120-NaOpushkeKomp-8</v>
-      </c>
-      <c r="C154" t="str">
-        <v/>
-      </c>
-      <c r="D154">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D154"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D153"/>
   </ignoredErrors>
 </worksheet>
 </file>